--- a/data/trans_orig/P16A_n_R2-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P16A_n_R2-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido dos o más medicamentos en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido dos o más medicamentos en las dos últimas semanas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6703</t>
+          <t>6628</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20208</t>
+          <t>20032</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>39848</t>
+          <t>39583</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>67008</t>
+          <t>64615</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>49961</t>
+          <t>49922</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>79528</t>
+          <t>80690</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,39%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>473856</t>
+          <t>474032</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>487361</t>
+          <t>487436</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>400481</t>
+          <t>402874</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>427641</t>
+          <t>427906</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>882025</t>
+          <t>880863</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>911592</t>
+          <t>911631</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,81%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18627</t>
+          <t>18568</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38997</t>
+          <t>39367</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>71803</t>
+          <t>71755</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>108181</t>
+          <t>108931</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>94895</t>
+          <t>95597</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>139237</t>
+          <t>136149</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,0%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>696492</t>
+          <t>696122</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>716862</t>
+          <t>716921</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>517313</t>
+          <t>516563</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>553691</t>
+          <t>553739</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1221745</t>
+          <t>1224833</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1266087</t>
+          <t>1265385</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>92,98%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41088</t>
+          <t>40612</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>67906</t>
+          <t>68498</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>81720</t>
+          <t>83936</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>121554</t>
+          <t>119577</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>130830</t>
+          <t>131283</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>175685</t>
+          <t>177910</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,39%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>570762</t>
+          <t>570170</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>597580</t>
+          <t>598056</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>568190</t>
+          <t>570167</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>608024</t>
+          <t>605808</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1152727</t>
+          <t>1150502</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1197582</t>
+          <t>1197129</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,12%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>64253</t>
+          <t>64733</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>97759</t>
+          <t>98549</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>103267</t>
+          <t>101366</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>140029</t>
+          <t>139444</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>172733</t>
+          <t>174610</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>226490</t>
+          <t>230353</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>22,26%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>421388</t>
+          <t>420598</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>454894</t>
+          <t>454414</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>81,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>375613</t>
+          <t>376198</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>412375</t>
+          <t>414276</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>72,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>80,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>808299</t>
+          <t>804436</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>862056</t>
+          <t>860179</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>77,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>83,13%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>113179</t>
+          <t>112892</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>149848</t>
+          <t>150179</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>158826</t>
+          <t>159291</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>198566</t>
+          <t>199538</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>39,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>49,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>283510</t>
+          <t>284366</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>338021</t>
+          <t>336885</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>42,61%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>236862</t>
+          <t>236531</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>273531</t>
+          <t>273818</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>61,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,73%</t>
+          <t>70,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>205420</t>
+          <t>204448</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>245160</t>
+          <t>244695</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>50,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>60,69%</t>
+          <t>60,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>452675</t>
+          <t>453811</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>507186</t>
+          <t>506330</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>57,25%</t>
+          <t>57,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>64,04%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>112699</t>
+          <t>115452</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>146951</t>
+          <t>147398</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>50,23%</t>
+          <t>50,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>205591</t>
+          <t>206079</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>238025</t>
+          <t>239919</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>60,09%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>69,96%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>331097</t>
+          <t>330142</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>378604</t>
+          <t>376477</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>51,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>59,24%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>145632</t>
+          <t>145185</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>179884</t>
+          <t>177131</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>49,77%</t>
+          <t>49,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>61,48%</t>
+          <t>60,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>104909</t>
+          <t>103015</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>137343</t>
+          <t>136855</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>256913</t>
+          <t>259040</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>304420</t>
+          <t>305375</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>47,9%</t>
+          <t>48,05%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>123309</t>
+          <t>124205</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>151170</t>
+          <t>152508</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>58,75%</t>
+          <t>59,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>72,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>225704</t>
+          <t>228089</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>259886</t>
+          <t>262017</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>67,59%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>359645</t>
+          <t>362293</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>404229</t>
+          <t>402326</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>73,99%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>58713</t>
+          <t>57375</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>86574</t>
+          <t>85678</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>74022</t>
+          <t>71891</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>108204</t>
+          <t>105819</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>139562</t>
+          <t>141465</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>184146</t>
+          <t>181498</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>33,38%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>528509</t>
+          <t>528764</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>612482</t>
+          <t>612259</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>951145</t>
+          <t>957519</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1064005</t>
+          <t>1062880</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1510894</t>
+          <t>1508901</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1648760</t>
+          <t>1646994</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,75%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2664061</t>
+          <t>2664284</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2748034</t>
+          <t>2747779</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2315192</t>
+          <t>2316317</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2428052</t>
+          <t>2421678</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>68,55%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5006981</t>
+          <t>5008747</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5144847</t>
+          <t>5146840</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>75,25%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>77,33%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido dos o más medicamentos en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido dos o más medicamentos en las dos últimas semanas en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15239</t>
+          <t>15714</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34908</t>
+          <t>35045</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>56043</t>
+          <t>54015</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>86928</t>
+          <t>84536</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>75692</t>
+          <t>75632</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>112586</t>
+          <t>111273</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,58%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>419238</t>
+          <t>419101</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>438907</t>
+          <t>438432</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>343302</t>
+          <t>345694</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>374187</t>
+          <t>376215</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,8%</t>
+          <t>80,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>771790</t>
+          <t>773103</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>808684</t>
+          <t>808744</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,45%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>52733</t>
+          <t>51689</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>83613</t>
+          <t>83771</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>103565</t>
+          <t>104118</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>145205</t>
+          <t>148224</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>166113</t>
+          <t>165491</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>215790</t>
+          <t>218484</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,84%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>603474</t>
+          <t>603316</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>634354</t>
+          <t>635398</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>465050</t>
+          <t>462031</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>506690</t>
+          <t>506137</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,21%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1081552</t>
+          <t>1078858</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1131229</t>
+          <t>1131851</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>87,24%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>68373</t>
+          <t>69890</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>104528</t>
+          <t>105011</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>148706</t>
+          <t>147910</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>194482</t>
+          <t>195121</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>232024</t>
+          <t>230977</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>290151</t>
+          <t>289120</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,76%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>577335</t>
+          <t>576852</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>613490</t>
+          <t>611973</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>516368</t>
+          <t>515729</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>562144</t>
+          <t>562940</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>72,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1102561</t>
+          <t>1103592</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1160688</t>
+          <t>1161735</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,42%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>90092</t>
+          <t>88890</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>130510</t>
+          <t>130316</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>179037</t>
+          <t>179935</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>229038</t>
+          <t>228208</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>280588</t>
+          <t>280985</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>342096</t>
+          <t>344677</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>28,0%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>484107</t>
+          <t>484301</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>524525</t>
+          <t>525727</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>387161</t>
+          <t>387991</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>437162</t>
+          <t>436264</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,83%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>70,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>888720</t>
+          <t>886139</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>950228</t>
+          <t>949831</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>72,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>77,17%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>155109</t>
+          <t>154555</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>195914</t>
+          <t>196254</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>45,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>230861</t>
+          <t>231996</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>274497</t>
+          <t>273518</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>51,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>61,3%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>397912</t>
+          <t>397841</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>459898</t>
+          <t>457108</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,43%</t>
+          <t>52,11%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>233515</t>
+          <t>233175</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>274320</t>
+          <t>274874</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>54,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>63,88%</t>
+          <t>64,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>173303</t>
+          <t>174282</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>216939</t>
+          <t>215804</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>417331</t>
+          <t>420121</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>479317</t>
+          <t>479388</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>47,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,64%</t>
+          <t>54,65%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>186966</t>
+          <t>187004</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>221819</t>
+          <t>222161</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>60,37%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>71,6%</t>
+          <t>71,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>244245</t>
+          <t>242528</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>278084</t>
+          <t>277139</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>442993</t>
+          <t>442763</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>492055</t>
+          <t>489918</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>73,81%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>87967</t>
+          <t>87625</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>122820</t>
+          <t>122782</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>75912</t>
+          <t>76857</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>109751</t>
+          <t>111468</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>171727</t>
+          <t>173864</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>220789</t>
+          <t>221019</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>33,3%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>185353</t>
+          <t>185467</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>211557</t>
+          <t>212682</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>325542</t>
+          <t>326445</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>352420</t>
+          <t>352595</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>516815</t>
+          <t>519551</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>555848</t>
+          <t>559131</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>81,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>87,52%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>38294</t>
+          <t>37169</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>64498</t>
+          <t>64384</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>36559</t>
+          <t>36384</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>63437</t>
+          <t>62534</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>82982</t>
+          <t>79699</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>122015</t>
+          <t>119279</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,67%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>815615</t>
+          <t>813379</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>920105</t>
+          <t>919139</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1365655</t>
+          <t>1364502</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1482575</t>
+          <t>1482274</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>41,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2210371</t>
+          <t>2212676</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2375709</t>
+          <t>2370765</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>33,94%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2506674</t>
+          <t>2507640</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2611164</t>
+          <t>2613400</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>73,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2075734</t>
+          <t>2076035</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2192654</t>
+          <t>2193807</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>58,33%</t>
+          <t>58,34%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>61,62%</t>
+          <t>61,65%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4609379</t>
+          <t>4614323</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4774717</t>
+          <t>4772412</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>66,06%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>68,32%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido dos o más medicamentos en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido dos o más medicamentos en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9233</t>
+          <t>9141</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25630</t>
+          <t>27046</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32759</t>
+          <t>31096</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>56858</t>
+          <t>58628</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46580</t>
+          <t>45294</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>75339</t>
+          <t>77087</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,46%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>393833</t>
+          <t>392417</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>410230</t>
+          <t>410322</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>338897</t>
+          <t>337127</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>362996</t>
+          <t>364659</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>739879</t>
+          <t>738131</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>768638</t>
+          <t>769924</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,44%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33383</t>
+          <t>33234</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>59959</t>
+          <t>62085</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>67302</t>
+          <t>68272</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>102275</t>
+          <t>100801</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>108176</t>
+          <t>110589</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>150822</t>
+          <t>151601</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,14%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>530537</t>
+          <t>528411</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>557113</t>
+          <t>557262</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>461269</t>
+          <t>462743</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>496242</t>
+          <t>495272</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1003218</t>
+          <t>1002439</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1045864</t>
+          <t>1043451</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>86,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>90,42%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>52577</t>
+          <t>52746</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>84574</t>
+          <t>84917</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>98081</t>
+          <t>96413</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>135278</t>
+          <t>134297</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>157592</t>
+          <t>160915</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>210166</t>
+          <t>211198</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,87%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>584523</t>
+          <t>584180</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>616520</t>
+          <t>616351</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>526108</t>
+          <t>527089</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>563305</t>
+          <t>564973</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>79,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1120317</t>
+          <t>1119285</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1172891</t>
+          <t>1169568</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>87,91%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>103578</t>
+          <t>103468</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>146830</t>
+          <t>146643</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>154027</t>
+          <t>152444</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>201767</t>
+          <t>200527</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>273684</t>
+          <t>268446</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>336053</t>
+          <t>332866</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,7%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>499218</t>
+          <t>499405</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>542470</t>
+          <t>542580</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>77,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>447310</t>
+          <t>448550</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>495050</t>
+          <t>496633</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>69,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>76,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>959072</t>
+          <t>962259</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1021441</t>
+          <t>1026679</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>74,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>79,27%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>143576</t>
+          <t>145398</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>187962</t>
+          <t>188618</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>39,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>236076</t>
+          <t>236514</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>285474</t>
+          <t>285488</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>47,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>392476</t>
+          <t>395520</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>461569</t>
+          <t>461631</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,35%</t>
+          <t>47,36%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>289956</t>
+          <t>289300</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>334342</t>
+          <t>332520</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>60,67%</t>
+          <t>60,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>69,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>211375</t>
+          <t>211361</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>260773</t>
+          <t>260335</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>52,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>513198</t>
+          <t>513136</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>582291</t>
+          <t>579247</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>52,65%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>59,74%</t>
+          <t>59,42%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>156239</t>
+          <t>156465</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>194099</t>
+          <t>193276</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>46,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>57,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>225091</t>
+          <t>225341</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>261368</t>
+          <t>261920</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>59,59%</t>
+          <t>59,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>69,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>390929</t>
+          <t>391817</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>444570</t>
+          <t>444999</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>55,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>62,43%</t>
+          <t>62,49%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>140231</t>
+          <t>141054</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>178091</t>
+          <t>177865</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>42,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>53,27%</t>
+          <t>53,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>116394</t>
+          <t>115842</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>152671</t>
+          <t>152421</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>267522</t>
+          <t>267093</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>321163</t>
+          <t>320275</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>44,98%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>170445</t>
+          <t>171444</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>196977</t>
+          <t>197248</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>66,32%</t>
+          <t>66,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>76,65%</t>
+          <t>76,75%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>292667</t>
+          <t>293538</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>328568</t>
+          <t>330068</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>471459</t>
+          <t>471842</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>517213</t>
+          <t>516324</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>78,57%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>60021</t>
+          <t>59750</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>86553</t>
+          <t>85554</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>71601</t>
+          <t>70101</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>107502</t>
+          <t>106631</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>139954</t>
+          <t>140843</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>185708</t>
+          <t>185325</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,2%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>730904</t>
+          <t>728195</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>829383</t>
+          <t>826325</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1172285</t>
+          <t>1179342</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1289757</t>
+          <t>1295341</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1937437</t>
+          <t>1929719</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2091778</t>
+          <t>2086393</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,07%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2564967</t>
+          <t>2568025</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2663446</t>
+          <t>2666155</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>75,57%</t>
+          <t>75,66%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>78,55%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2254785</t>
+          <t>2249201</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2372257</t>
+          <t>2365200</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>63,61%</t>
+          <t>63,46%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>66,93%</t>
+          <t>66,73%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4847114</t>
+          <t>4852499</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5001455</t>
+          <t>5009173</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>72,19%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido dos o más medicamentos en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido dos o más medicamentos en las dos últimas semanas en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17571</t>
+          <t>18397</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>58754</t>
+          <t>58586</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26685</t>
+          <t>28744</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>62559</t>
+          <t>60751</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>55436</t>
+          <t>55393</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>106108</t>
+          <t>110336</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>15,47%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>341233</t>
+          <t>341401</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>382416</t>
+          <t>381590</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>250641</t>
+          <t>252449</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>286515</t>
+          <t>284456</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>80,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>607079</t>
+          <t>602851</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>657751</t>
+          <t>657794</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,7 +9868,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36178</t>
+          <t>36045</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>71287</t>
+          <t>72164</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51964</t>
+          <t>51919</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>108110</t>
+          <t>106845</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>101651</t>
+          <t>103010</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>163770</t>
+          <t>163451</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,47%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>352260</t>
+          <t>351383</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>387369</t>
+          <t>387502</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>403983</t>
+          <t>405248</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>460129</t>
+          <t>460174</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>79,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>771870</t>
+          <t>772189</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>833989</t>
+          <t>832630</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>88,99%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>63305</t>
+          <t>61738</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>97915</t>
+          <t>93690</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>94571</t>
+          <t>89228</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>142847</t>
+          <t>140463</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>166380</t>
+          <t>169275</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>224866</t>
+          <t>223476</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,81%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>438423</t>
+          <t>442648</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>473033</t>
+          <t>474600</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>449155</t>
+          <t>451539</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>497431</t>
+          <t>502774</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>76,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>84,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>903474</t>
+          <t>904864</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>961960</t>
+          <t>959065</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,0%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>74930</t>
+          <t>78272</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>247129</t>
+          <t>249959</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>197282</t>
+          <t>198011</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>258458</t>
+          <t>258104</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>234569</t>
+          <t>252821</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>497320</t>
+          <t>498647</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>31,15%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>640657</t>
+          <t>637827</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>812856</t>
+          <t>809514</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,16%</t>
+          <t>71,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>454423</t>
+          <t>454777</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>515599</t>
+          <t>514870</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>63,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1103347</t>
+          <t>1102020</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1366098</t>
+          <t>1347846</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,93%</t>
+          <t>68,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>84,21%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>215319</t>
+          <t>217095</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>261655</t>
+          <t>258523</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>266524</t>
+          <t>264900</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>301408</t>
+          <t>301443</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>48,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,01%</t>
+          <t>55,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>488829</t>
+          <t>491159</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>546344</t>
+          <t>548122</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,26%</t>
+          <t>49,42%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>299579</t>
+          <t>302711</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>345915</t>
+          <t>344139</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>53,38%</t>
+          <t>53,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,63%</t>
+          <t>61,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>246497</t>
+          <t>246462</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>281381</t>
+          <t>283005</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>44,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>51,36%</t>
+          <t>51,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>562795</t>
+          <t>561017</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>620310</t>
+          <t>617980</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
+          <t>50,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>55,72%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>179159</t>
+          <t>179567</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>209511</t>
+          <t>211048</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>48,77%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>56,91%</t>
+          <t>57,32%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>399999</t>
+          <t>398370</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>553912</t>
+          <t>547344</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>581849</t>
+          <t>581067</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>806115</t>
+          <t>810523</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>59,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>83,0%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>158654</t>
+          <t>157117</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>189006</t>
+          <t>188598</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>51,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>54456</t>
+          <t>61024</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>208369</t>
+          <t>209998</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>170418</t>
+          <t>166010</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>394684</t>
+          <t>395466</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>40,5%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>180911</t>
+          <t>179636</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>205486</t>
+          <t>205447</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>63,98%</t>
+          <t>63,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>72,67%</t>
+          <t>72,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>333922</t>
+          <t>333523</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>357335</t>
+          <t>356658</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>78,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>519847</t>
+          <t>520694</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>554594</t>
+          <t>555924</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>73,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>78,45%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>77273</t>
+          <t>77312</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>101848</t>
+          <t>103123</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>68496</t>
+          <t>69173</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>91909</t>
+          <t>92308</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>153996</t>
+          <t>152666</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>188743</t>
+          <t>187896</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,52%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>769346</t>
+          <t>738827</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1057510</t>
+          <t>1054383</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1435776</t>
+          <t>1433857</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2015906</t>
+          <t>1977414</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>53,27%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2299674</t>
+          <t>2316995</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3002654</t>
+          <t>2933743</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>40,9%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2402307</t>
+          <t>2405434</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2690471</t>
+          <t>2720990</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>69,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>78,65%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1696374</t>
+          <t>1734866</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2276504</t>
+          <t>2278423</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>46,73%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>61,38%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4169443</t>
+          <t>4238354</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4872423</t>
+          <t>4855102</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>59,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>67,69%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A_n_R2-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P16A_n_R2-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6628</t>
+          <t>6910</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20032</t>
+          <t>20963</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>39583</t>
+          <t>39461</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>64615</t>
+          <t>65002</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>49922</t>
+          <t>50704</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>80690</t>
+          <t>79542</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,27%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>474032</t>
+          <t>473101</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>487436</t>
+          <t>487154</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>402874</t>
+          <t>402487</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>427906</t>
+          <t>428028</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>880863</t>
+          <t>882011</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>911631</t>
+          <t>910849</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,73%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18568</t>
+          <t>17970</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39367</t>
+          <t>37356</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>71755</t>
+          <t>71025</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>108931</t>
+          <t>107506</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>95597</t>
+          <t>95838</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>136149</t>
+          <t>137069</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,07%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>696122</t>
+          <t>698133</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>716921</t>
+          <t>717519</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>516563</t>
+          <t>517988</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>553739</t>
+          <t>554469</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1224833</t>
+          <t>1223913</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1265385</t>
+          <t>1265144</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,96%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>40612</t>
+          <t>42520</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>68498</t>
+          <t>68568</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>83936</t>
+          <t>82010</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>119577</t>
+          <t>119887</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>131283</t>
+          <t>130431</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>177910</t>
+          <t>177853</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>570170</t>
+          <t>570100</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>598056</t>
+          <t>596148</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>570167</t>
+          <t>569857</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>605808</t>
+          <t>607734</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1150502</t>
+          <t>1150559</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1197129</t>
+          <t>1197981</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>90,18%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>64733</t>
+          <t>62773</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>98549</t>
+          <t>96679</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>101366</t>
+          <t>102039</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>139444</t>
+          <t>139683</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>174610</t>
+          <t>176226</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>230353</t>
+          <t>225200</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>21,76%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>420598</t>
+          <t>422468</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>454414</t>
+          <t>456374</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>376198</t>
+          <t>375959</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>414276</t>
+          <t>413603</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,96%</t>
+          <t>72,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>804436</t>
+          <t>809589</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>860179</t>
+          <t>858563</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>78,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>82,97%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>112892</t>
+          <t>114608</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>150179</t>
+          <t>149332</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>159291</t>
+          <t>158416</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>199538</t>
+          <t>198725</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,39%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>284366</t>
+          <t>285184</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>336885</t>
+          <t>341169</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>43,15%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>236531</t>
+          <t>237378</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>273818</t>
+          <t>272102</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>61,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>70,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>204448</t>
+          <t>205261</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>244695</t>
+          <t>245570</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>50,61%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>60,57%</t>
+          <t>60,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>453811</t>
+          <t>449527</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>506330</t>
+          <t>505512</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>56,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>63,93%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>115452</t>
+          <t>113816</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>147398</t>
+          <t>146438</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>50,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>206079</t>
+          <t>205613</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>239919</t>
+          <t>238786</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>59,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>69,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>330142</t>
+          <t>328338</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>376477</t>
+          <t>377510</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>59,24%</t>
+          <t>59,4%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>145185</t>
+          <t>146145</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>177131</t>
+          <t>178767</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>49,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>61,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>103015</t>
+          <t>104148</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>136855</t>
+          <t>137321</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>259040</t>
+          <t>258007</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>305375</t>
+          <t>307179</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>40,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>48,34%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>124205</t>
+          <t>124782</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>152508</t>
+          <t>151151</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>59,18%</t>
+          <t>59,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>72,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>228089</t>
+          <t>225411</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>262017</t>
+          <t>259411</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>68,31%</t>
+          <t>67,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>362293</t>
+          <t>358862</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>402326</t>
+          <t>401570</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>65,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>73,85%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>57375</t>
+          <t>58732</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>85678</t>
+          <t>85101</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>71891</t>
+          <t>74497</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>105819</t>
+          <t>108497</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>141465</t>
+          <t>142221</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>181498</t>
+          <t>184929</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>34,01%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>528764</t>
+          <t>531817</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>612259</t>
+          <t>613638</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>957519</t>
+          <t>956577</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1062880</t>
+          <t>1067183</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1508901</t>
+          <t>1507175</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1646994</t>
+          <t>1650446</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,8%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2664284</t>
+          <t>2662905</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2747779</t>
+          <t>2744726</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>81,27%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2316317</t>
+          <t>2312014</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2421678</t>
+          <t>2422620</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>68,55%</t>
+          <t>68,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,69%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5008747</t>
+          <t>5005295</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5146840</t>
+          <t>5148566</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>77,36%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15714</t>
+          <t>15227</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35045</t>
+          <t>34572</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>54015</t>
+          <t>53846</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>84536</t>
+          <t>83778</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>75632</t>
+          <t>77423</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>111273</t>
+          <t>112461</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,72%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>419101</t>
+          <t>419574</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>438432</t>
+          <t>438919</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>345694</t>
+          <t>346452</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>376215</t>
+          <t>376384</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>80,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>773103</t>
+          <t>771915</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>808744</t>
+          <t>806953</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,25%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>51689</t>
+          <t>53161</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>83771</t>
+          <t>84276</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>104118</t>
+          <t>103413</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>148224</t>
+          <t>144079</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>165491</t>
+          <t>166441</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>218484</t>
+          <t>220052</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,96%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>603316</t>
+          <t>602811</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>635398</t>
+          <t>633926</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>462031</t>
+          <t>466176</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>506137</t>
+          <t>506842</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1078858</t>
+          <t>1077290</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1131851</t>
+          <t>1130901</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>83,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>87,17%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>69890</t>
+          <t>70184</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>105011</t>
+          <t>106432</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>147910</t>
+          <t>149754</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>195121</t>
+          <t>195417</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>230977</t>
+          <t>229597</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>289120</t>
+          <t>289084</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>576852</t>
+          <t>575431</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>611973</t>
+          <t>611679</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>515729</t>
+          <t>515433</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>562940</t>
+          <t>561096</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>72,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>78,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1103592</t>
+          <t>1103628</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1161735</t>
+          <t>1163115</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4601,7 +4601,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>83,51%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>88890</t>
+          <t>89975</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>130316</t>
+          <t>129363</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>179935</t>
+          <t>182142</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>228208</t>
+          <t>228525</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>280985</t>
+          <t>279945</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>344677</t>
+          <t>344886</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>28,02%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>484301</t>
+          <t>485254</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>525727</t>
+          <t>524642</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>387991</t>
+          <t>387674</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>436264</t>
+          <t>434057</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,97%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>70,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>886139</t>
+          <t>885930</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>949831</t>
+          <t>950871</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>71,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>77,26%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>154555</t>
+          <t>155022</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>196254</t>
+          <t>198421</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>231996</t>
+          <t>232407</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>273518</t>
+          <t>275992</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>51,81%</t>
+          <t>51,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>61,08%</t>
+          <t>61,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>397841</t>
+          <t>398930</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>457108</t>
+          <t>459943</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>45,35%</t>
+          <t>45,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>52,43%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>233175</t>
+          <t>231008</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>274874</t>
+          <t>274407</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>53,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>64,01%</t>
+          <t>63,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>174282</t>
+          <t>171808</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>215804</t>
+          <t>215393</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>48,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>420121</t>
+          <t>417286</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>479388</t>
+          <t>478299</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>47,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,65%</t>
+          <t>54,52%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>187004</t>
+          <t>188944</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>222161</t>
+          <t>223900</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>60,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>72,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>242528</t>
+          <t>242811</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>277139</t>
+          <t>277035</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>68,59%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>78,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>442763</t>
+          <t>444151</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>489918</t>
+          <t>491220</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>66,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>74,0%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>87625</t>
+          <t>85886</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>122782</t>
+          <t>120842</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>76857</t>
+          <t>76961</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>111468</t>
+          <t>111185</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>173864</t>
+          <t>172562</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>221019</t>
+          <t>219631</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,09%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>185467</t>
+          <t>185096</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>212682</t>
+          <t>211287</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>74,23%</t>
+          <t>74,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>326445</t>
+          <t>325300</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>352595</t>
+          <t>353616</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>519551</t>
+          <t>518835</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>559131</t>
+          <t>556255</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,07%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>37169</t>
+          <t>38564</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>64384</t>
+          <t>64755</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>36384</t>
+          <t>35363</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>62534</t>
+          <t>63679</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>79699</t>
+          <t>82575</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>119279</t>
+          <t>119995</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,78%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>813379</t>
+          <t>809215</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>919139</t>
+          <t>914675</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1364502</t>
+          <t>1369206</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1482274</t>
+          <t>1483275</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2212676</t>
+          <t>2210844</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2370765</t>
+          <t>2366137</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>33,87%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2507640</t>
+          <t>2512104</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2613400</t>
+          <t>2617564</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2076035</t>
+          <t>2075034</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2193807</t>
+          <t>2189103</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>58,34%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>61,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4614323</t>
+          <t>4618951</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4772412</t>
+          <t>4774244</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>66,06%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>68,35%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9141</t>
+          <t>8342</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27046</t>
+          <t>26506</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31096</t>
+          <t>32629</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>58628</t>
+          <t>57600</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>45294</t>
+          <t>45574</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>77087</t>
+          <t>76203</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,35%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>392417</t>
+          <t>392957</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>410322</t>
+          <t>411121</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>337127</t>
+          <t>338155</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>364659</t>
+          <t>363126</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>738131</t>
+          <t>739015</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>769924</t>
+          <t>769644</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,41%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33234</t>
+          <t>34874</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>62085</t>
+          <t>59682</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>68272</t>
+          <t>65759</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>100801</t>
+          <t>99111</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>110589</t>
+          <t>108716</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>151601</t>
+          <t>152074</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,18%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>528411</t>
+          <t>530814</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>557262</t>
+          <t>555622</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>462743</t>
+          <t>464433</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>495272</t>
+          <t>497785</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1002439</t>
+          <t>1001966</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1043451</t>
+          <t>1045324</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,58%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>52746</t>
+          <t>53062</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>84917</t>
+          <t>84535</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>96413</t>
+          <t>97088</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>134297</t>
+          <t>135307</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>160915</t>
+          <t>159837</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>211198</t>
+          <t>209295</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,73%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>584180</t>
+          <t>584562</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>616351</t>
+          <t>616035</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>527089</t>
+          <t>526079</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>564973</t>
+          <t>564298</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1119285</t>
+          <t>1121188</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1169568</t>
+          <t>1170646</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,99%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>103468</t>
+          <t>103034</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>146643</t>
+          <t>144454</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>152444</t>
+          <t>155153</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>200527</t>
+          <t>201934</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>268446</t>
+          <t>273799</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>332866</t>
+          <t>336784</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>26,0%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>499405</t>
+          <t>501594</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>542580</t>
+          <t>543014</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>77,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>84,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>448550</t>
+          <t>447143</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>496633</t>
+          <t>493924</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,11%</t>
+          <t>68,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>962259</t>
+          <t>958341</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1026679</t>
+          <t>1021326</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>78,86%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>145398</t>
+          <t>144166</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>188618</t>
+          <t>187567</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>236514</t>
+          <t>236984</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>285488</t>
+          <t>283666</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>47,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,46%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>395520</t>
+          <t>394828</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>461631</t>
+          <t>459123</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>47,1%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>289300</t>
+          <t>290351</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>332520</t>
+          <t>333752</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>60,53%</t>
+          <t>60,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>69,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>211361</t>
+          <t>213183</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>260335</t>
+          <t>259865</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>52,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>513136</t>
+          <t>515644</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>579247</t>
+          <t>579939</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>52,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>59,5%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>156465</t>
+          <t>158813</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>193276</t>
+          <t>194631</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>57,81%</t>
+          <t>58,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>225341</t>
+          <t>222711</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>261920</t>
+          <t>260569</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>58,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>69,33%</t>
+          <t>68,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>391817</t>
+          <t>393476</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>444999</t>
+          <t>446177</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>55,26%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>62,66%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>141054</t>
+          <t>139699</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>177865</t>
+          <t>175517</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>53,2%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>115842</t>
+          <t>117193</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>152421</t>
+          <t>155051</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>41,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>267093</t>
+          <t>265915</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>320275</t>
+          <t>318616</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>44,74%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>171444</t>
+          <t>171155</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>197248</t>
+          <t>196339</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>66,71%</t>
+          <t>66,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>76,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>293538</t>
+          <t>291721</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>330068</t>
+          <t>329562</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>73,35%</t>
+          <t>72,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>82,48%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>471842</t>
+          <t>470226</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>516324</t>
+          <t>518029</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,83%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>59750</t>
+          <t>60659</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>85554</t>
+          <t>85843</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>70101</t>
+          <t>70607</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>106631</t>
+          <t>108448</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>140843</t>
+          <t>139138</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>185325</t>
+          <t>186941</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,45%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>728195</t>
+          <t>731051</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>826325</t>
+          <t>828740</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1179342</t>
+          <t>1177292</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1295341</t>
+          <t>1295952</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1929719</t>
+          <t>1938917</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2086393</t>
+          <t>2087176</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,08%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2568025</t>
+          <t>2565610</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2666155</t>
+          <t>2663299</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>78,46%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2249201</t>
+          <t>2248590</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2365200</t>
+          <t>2367250</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>63,46%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>66,79%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4852499</t>
+          <t>4851716</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5009173</t>
+          <t>4999975</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>69,92%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>72,06%</t>
         </is>
       </c>
     </row>
@@ -9665,32 +9665,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>33796</t>
+          <t>38471</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18397</t>
+          <t>22446</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>58586</t>
+          <t>61304</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>42624</t>
+          <t>53799</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28744</t>
+          <t>36099</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>60751</t>
+          <t>76382</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>76419</t>
+          <t>92270</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>55393</t>
+          <t>69788</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>110336</t>
+          <t>124084</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>16,11%</t>
         </is>
       </c>
     </row>
@@ -9778,32 +9778,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>366191</t>
+          <t>369322</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>341401</t>
+          <t>346489</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>381590</t>
+          <t>385347</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>84,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>270576</t>
+          <t>308713</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>252449</t>
+          <t>286130</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>284456</t>
+          <t>326413</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>78,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>636768</t>
+          <t>678035</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>602851</t>
+          <t>646221</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>657794</t>
+          <t>700517</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>90,94%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>51505</t>
+          <t>59823</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36045</t>
+          <t>41399</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>72164</t>
+          <t>80875</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>84230</t>
+          <t>88453</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51919</t>
+          <t>71417</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>106845</t>
+          <t>109368</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>135734</t>
+          <t>148276</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>103010</t>
+          <t>123815</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>163451</t>
+          <t>176967</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>18,08%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>372042</t>
+          <t>417067</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>351383</t>
+          <t>396015</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>387502</t>
+          <t>435491</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>83,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>427863</t>
+          <t>413280</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>405248</t>
+          <t>392365</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>460174</t>
+          <t>430316</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>78,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>799906</t>
+          <t>830347</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>772189</t>
+          <t>801656</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>832630</t>
+          <t>854808</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>87,35%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>77370</t>
+          <t>86715</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>61738</t>
+          <t>69288</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>93690</t>
+          <t>106018</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>121025</t>
+          <t>136165</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>89228</t>
+          <t>120069</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>140463</t>
+          <t>155517</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>198394</t>
+          <t>222879</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>169275</t>
+          <t>198160</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>223476</t>
+          <t>249985</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>20,09%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>458968</t>
+          <t>534122</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>442648</t>
+          <t>514819</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>474600</t>
+          <t>551549</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>82,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>470977</t>
+          <t>487028</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>451539</t>
+          <t>467676</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>502774</t>
+          <t>503124</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>75,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>929946</t>
+          <t>1021150</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>904864</t>
+          <t>994044</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>959065</t>
+          <t>1045869</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>84,07%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>172157</t>
+          <t>186105</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>78272</t>
+          <t>162821</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>249959</t>
+          <t>209762</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>235686</t>
+          <t>248345</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>198011</t>
+          <t>226821</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>258104</t>
+          <t>269229</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>407843</t>
+          <t>434451</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>252821</t>
+          <t>404075</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>498647</t>
+          <t>466144</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>32,43%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>715629</t>
+          <t>514512</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>637827</t>
+          <t>490855</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>809514</t>
+          <t>537796</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>73,44%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>70,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>477195</t>
+          <t>488541</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>454777</t>
+          <t>467657</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>514870</t>
+          <t>510065</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>66,94%</t>
+          <t>66,3%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>63,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>69,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1192824</t>
+          <t>1003053</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1102020</t>
+          <t>971360</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1347846</t>
+          <t>1033429</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>74,52%</t>
+          <t>69,78%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,85%</t>
+          <t>67,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>71,89%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>236925</t>
+          <t>251065</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>217095</t>
+          <t>228027</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>258523</t>
+          <t>273939</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,06%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>283409</t>
+          <t>315746</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>264900</t>
+          <t>296308</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>301443</t>
+          <t>335769</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>51,73%</t>
+          <t>51,86%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>48,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>55,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>520334</t>
+          <t>566811</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>491159</t>
+          <t>536155</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>548122</t>
+          <t>595808</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>46,91%</t>
+          <t>46,53%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>48,91%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>324309</t>
+          <t>358281</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>302711</t>
+          <t>335407</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>344139</t>
+          <t>381319</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>57,79%</t>
+          <t>58,8%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>53,94%</t>
+          <t>55,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>62,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>264496</t>
+          <t>293109</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>246462</t>
+          <t>273086</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>283005</t>
+          <t>312547</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>48,14%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>44,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>51,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>588805</t>
+          <t>651391</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>561017</t>
+          <t>622394</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>617980</t>
+          <t>682047</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>53,09%</t>
+          <t>53,47%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>51,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>55,72%</t>
+          <t>55,99%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>196215</t>
+          <t>213729</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>179567</t>
+          <t>197068</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>211048</t>
+          <t>233000</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>53,3%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>48,41%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>57,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>474296</t>
+          <t>294050</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>398370</t>
+          <t>280010</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>547344</t>
+          <t>308574</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>66,96%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>65,48%</t>
+          <t>63,76%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>70,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>670511</t>
+          <t>507779</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>581067</t>
+          <t>485203</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>810523</t>
+          <t>531344</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>60,0%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>57,34%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>62,79%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>171950</t>
+          <t>193351</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>157117</t>
+          <t>174080</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>188598</t>
+          <t>210012</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>46,7%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>42,76%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>51,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>134072</t>
+          <t>145116</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>61024</t>
+          <t>130592</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>209998</t>
+          <t>159156</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>306022</t>
+          <t>338467</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>166010</t>
+          <t>314902</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>395466</t>
+          <t>361043</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>42,66%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>193364</t>
+          <t>210655</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>179636</t>
+          <t>196610</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>205447</t>
+          <t>225999</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>67,91%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>63,53%</t>
+          <t>63,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>72,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>345399</t>
+          <t>374768</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>333523</t>
+          <t>360941</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>356658</t>
+          <t>386822</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>80,66%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>538763</t>
+          <t>585423</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>520694</t>
+          <t>565339</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>555924</t>
+          <t>605423</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>72,97%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>78,14%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>89395</t>
+          <t>99543</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>77312</t>
+          <t>84199</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>103123</t>
+          <t>113588</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>80432</t>
+          <t>89841</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>69173</t>
+          <t>77787</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>92308</t>
+          <t>103668</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>169827</t>
+          <t>189384</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>152666</t>
+          <t>169384</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>187896</t>
+          <t>209468</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>27,03%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>961331</t>
+          <t>1046564</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>738827</t>
+          <t>991785</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1054383</t>
+          <t>1110818</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1586668</t>
+          <t>1511326</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1433857</t>
+          <t>1459245</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1977414</t>
+          <t>1566536</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>53,27%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>2547999</t>
+          <t>2557890</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2316995</t>
+          <t>2475849</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2933743</t>
+          <t>2636790</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>36,27%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2498486</t>
+          <t>2486198</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2405434</t>
+          <t>2421944</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2720990</t>
+          <t>2540977</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>70,38%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2125612</t>
+          <t>2225628</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1734866</t>
+          <t>2170418</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2278423</t>
+          <t>2277709</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>57,26%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>58,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>61,38%</t>
+          <t>60,95%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>4624098</t>
+          <t>4711826</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4238354</t>
+          <t>4632926</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4855102</t>
+          <t>4793867</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>64,81%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>63,73%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>65,94%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
